--- a/artfynd/A 25020-2026 artfynd.xlsx
+++ b/artfynd/A 25020-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86583442</v>
+        <v>86583441</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410266.0806949603</v>
+        <v>410257</v>
       </c>
       <c r="R2" t="n">
-        <v>6597471.977378626</v>
+        <v>6597474</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2020-04-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-04-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,6 +784,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>86583442</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Illberg -Norra hyn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>410266</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6597472</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-04-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-04-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Död på väg. Groddjursinventering Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25020-2026 artfynd.xlsx
+++ b/artfynd/A 25020-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86583441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,8 +906,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86583442</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>